--- a/data/trans_dic/IP24_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que no hacen ejercicio</t>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,3; 32,82</t>
+          <t>17,21; 32,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 24,87</t>
+          <t>11,32; 24,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,01; 31,93</t>
+          <t>13,62; 32,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,15; 52,83</t>
+          <t>16,21; 52,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 26,99</t>
+          <t>13,57; 26,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 19,48</t>
+          <t>7,44; 19,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 18,15</t>
+          <t>6,19; 18,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 33,33</t>
+          <t>13,74; 33,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,83; 27,4</t>
+          <t>17,58; 27,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 19,84</t>
+          <t>10,81; 19,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 22,11</t>
+          <t>11,13; 22,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,0; 38,82</t>
+          <t>18,65; 39,91</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,6; 29,38</t>
+          <t>22,81; 29,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,68; 25,0</t>
+          <t>18,88; 25,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 24,83</t>
+          <t>18,49; 25,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,82; 41,99</t>
+          <t>18,83; 38,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,45; 25,7</t>
+          <t>19,66; 25,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,59; 19,12</t>
+          <t>13,49; 19,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 17,74</t>
+          <t>12,21; 17,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 23,98</t>
+          <t>14,6; 23,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,99; 26,49</t>
+          <t>21,96; 26,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 20,84</t>
+          <t>16,99; 21,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 20,23</t>
+          <t>16,06; 20,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 29,03</t>
+          <t>17,58; 29,67</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,96; 29,41</t>
+          <t>19,33; 29,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 24,0</t>
+          <t>13,29; 23,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 28,15</t>
+          <t>17,79; 27,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 23,04</t>
+          <t>12,27; 22,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,4; 33,01</t>
+          <t>22,16; 33,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,48; 22,04</t>
+          <t>12,58; 22,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,6; 29,74</t>
+          <t>19,52; 29,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 21,96</t>
+          <t>11,6; 21,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,74; 29,92</t>
+          <t>21,61; 29,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,46; 21,33</t>
+          <t>14,54; 21,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,77; 27,65</t>
+          <t>19,97; 27,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,55; 20,44</t>
+          <t>13,16; 20,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 28,02</t>
+          <t>22,61; 27,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 22,89</t>
+          <t>17,9; 22,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,51; 24,36</t>
+          <t>19,45; 24,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,04; 35,1</t>
+          <t>18,91; 35,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,86; 25,87</t>
+          <t>20,97; 25,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,78; 18,21</t>
+          <t>13,97; 18,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,0</t>
+          <t>14,83; 19,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,47</t>
+          <t>15,31; 22,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,61; 26,42</t>
+          <t>22,59; 26,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,42; 19,73</t>
+          <t>16,43; 19,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,64; 21,0</t>
+          <t>17,73; 21,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 25,45</t>
+          <t>17,76; 25,84</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22127</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15730</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12996</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17409</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10376</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13928</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>39535</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26106</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20532</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>30816</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>15530; 28937</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10304; 22251</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8087; 19128</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8863; 28794</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11786; 23203</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6234; 16391</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4204; 12607</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8391; 20393</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>31125; 48916</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>18894; 34608</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14174; 28564</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>21582; 46197</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>108323</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>97610</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>102538</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112812</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>107513</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79312</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71303</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>91962</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>215836</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>176922</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>173841</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>204774</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>94756; 124461</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>84538; 112531</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87098; 117850</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>86265; 176241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>93660; 121935</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>65938; 94703</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>59388; 83500</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>75042; 121635</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>195822; 236276</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>159176; 198201</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>153776; 192355</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>170887; 288500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>41281</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30110</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>38833</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25695</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>43225</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28759</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45566</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>29610</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>84505</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58869</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>84398</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>55306</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>33500; 50610</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22166; 38365</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30719; 47925</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18346; 33958</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>34906; 52923</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>21366; 37658</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>36354; 54934</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>21187; 39648</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>71478; 97354</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>48936; 72426</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>71684; 98908</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>43713; 67393</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>171730</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>143451</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>154366</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>155395</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>168147</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>135501</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>339877</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>261896</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>278770</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>290896</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>153497; 189808</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>126335; 161135</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>136754; 171778</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>125294; 237599</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>151082; 186581</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>103709; 136198</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>109816; 142331</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>116013; 169253</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>316124; 366254</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>237962; 285573</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>255880; 304123</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>252212; 367025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP24_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,21; 32,07</t>
+          <t>18,24; 32,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,32; 24,44</t>
+          <t>11,66; 24,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,62; 32,21</t>
+          <t>14,03; 32,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,21; 52,66</t>
+          <t>17,53; 55,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,57; 26,72</t>
+          <t>14,15; 27,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 19,58</t>
+          <t>7,24; 19,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 18,56</t>
+          <t>5,63; 18,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,74; 33,39</t>
+          <t>14,21; 33,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,58; 27,62</t>
+          <t>17,5; 27,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,81; 19,8</t>
+          <t>10,42; 19,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,13; 22,44</t>
+          <t>11,29; 22,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,65; 39,91</t>
+          <t>18,56; 39,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,81; 29,96</t>
+          <t>22,7; 29,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,88; 25,13</t>
+          <t>18,46; 24,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 25,02</t>
+          <t>19,02; 24,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 38,47</t>
+          <t>18,74; 38,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,66; 25,6</t>
+          <t>19,8; 25,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,38</t>
+          <t>13,66; 18,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 17,17</t>
+          <t>12,29; 17,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 23,66</t>
+          <t>14,66; 24,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,96; 26,5</t>
+          <t>21,88; 26,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,99; 21,16</t>
+          <t>16,85; 21,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,06; 20,09</t>
+          <t>16,26; 20,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,58; 29,67</t>
+          <t>17,41; 27,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,33; 29,2</t>
+          <t>19,13; 29,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,29; 23,0</t>
+          <t>13,66; 23,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,79; 27,75</t>
+          <t>17,61; 27,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,27; 22,71</t>
+          <t>12,34; 23,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,16; 33,6</t>
+          <t>22,58; 33,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,58; 22,18</t>
+          <t>12,55; 22,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,52; 29,5</t>
+          <t>19,77; 29,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 21,72</t>
+          <t>11,89; 21,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,61; 29,43</t>
+          <t>21,94; 29,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,54; 21,52</t>
+          <t>14,47; 21,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,97; 27,56</t>
+          <t>20,08; 27,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,16; 20,29</t>
+          <t>13,43; 20,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,61; 27,96</t>
+          <t>22,76; 27,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 22,83</t>
+          <t>17,86; 22,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,43</t>
+          <t>19,44; 24,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 35,87</t>
+          <t>18,63; 34,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,97; 25,89</t>
+          <t>20,72; 25,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 18,35</t>
+          <t>13,77; 18,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,83; 19,22</t>
+          <t>14,58; 18,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,31; 22,34</t>
+          <t>15,28; 22,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,59; 26,17</t>
+          <t>22,41; 26,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,43; 19,72</t>
+          <t>16,46; 19,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,73; 21,07</t>
+          <t>17,7; 20,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,76; 25,84</t>
+          <t>17,91; 25,82</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15530; 28937</t>
+          <t>16458; 29014</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10304; 22251</t>
+          <t>10614; 22585</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8087; 19128</t>
+          <t>8330; 19447</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8863; 28794</t>
+          <t>9587; 30478</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11786; 23203</t>
+          <t>12285; 23736</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6234; 16391</t>
+          <t>6063; 16218</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4204; 12607</t>
+          <t>3825; 12547</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8391; 20393</t>
+          <t>8679; 20357</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31125; 48916</t>
+          <t>30981; 49502</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18894; 34608</t>
+          <t>18207; 33721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14174; 28564</t>
+          <t>14377; 28457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21582; 46197</t>
+          <t>21483; 45587</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94756; 124461</t>
+          <t>94289; 123397</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84538; 112531</t>
+          <t>82659; 111240</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87098; 117850</t>
+          <t>89564; 117629</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86265; 176241</t>
+          <t>85871; 176869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93660; 121935</t>
+          <t>94300; 122350</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65938; 94703</t>
+          <t>66771; 92834</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59388; 83500</t>
+          <t>59781; 87051</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75042; 121635</t>
+          <t>75371; 124536</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>195822; 236276</t>
+          <t>195113; 236447</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>159176; 198201</t>
+          <t>157831; 197125</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153776; 192355</t>
+          <t>155657; 193825</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>170887; 288500</t>
+          <t>169247; 271527</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33500; 50610</t>
+          <t>33165; 50880</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22166; 38365</t>
+          <t>22783; 39364</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30719; 47925</t>
+          <t>30405; 48152</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18346; 33958</t>
+          <t>18460; 34545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34906; 52923</t>
+          <t>35560; 52508</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21366; 37658</t>
+          <t>21316; 37647</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36354; 54934</t>
+          <t>36813; 55035</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21187; 39648</t>
+          <t>21715; 39336</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71478; 97354</t>
+          <t>72573; 97671</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48936; 72426</t>
+          <t>48713; 70845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71684; 98908</t>
+          <t>72069; 97788</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43713; 67393</t>
+          <t>44611; 67025</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>153497; 189808</t>
+          <t>154519; 189953</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126335; 161135</t>
+          <t>126031; 160032</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136754; 171778</t>
+          <t>136692; 172716</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125294; 237599</t>
+          <t>123419; 227771</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>151082; 186581</t>
+          <t>149294; 186591</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>103709; 136198</t>
+          <t>102240; 135423</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109816; 142331</t>
+          <t>108004; 139898</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>116013; 169253</t>
+          <t>115769; 168429</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>316124; 366254</t>
+          <t>313624; 366695</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237962; 285573</t>
+          <t>238331; 288270</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>255880; 304123</t>
+          <t>255509; 302504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>252212; 367025</t>
+          <t>254374; 366625</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,39%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24,52%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>17,27%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>21,89%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 32,15</t>
+          <t>12,99; 26,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,66; 24,8</t>
+          <t>7,49; 19,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 32,75</t>
+          <t>5,55; 18,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,53; 55,74</t>
+          <t>12,57; 30,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,15; 27,33</t>
+          <t>17,3; 32,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 19,37</t>
+          <t>11,18; 24,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 18,48</t>
+          <t>14,01; 31,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 33,33</t>
+          <t>11,64; 30,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,5; 27,95</t>
+          <t>17,83; 27,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 19,29</t>
+          <t>10,7; 19,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,29; 22,36</t>
+          <t>11,46; 22,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,56; 39,39</t>
+          <t>14,14; 26,8</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,57%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>26,08%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>21,79%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>21,77%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,57%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,7; 29,71</t>
+          <t>19,45; 25,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,46; 24,84</t>
+          <t>13,59; 19,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,02; 24,98</t>
+          <t>12,37; 17,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,74; 38,6</t>
+          <t>13,35; 21,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,8; 25,69</t>
+          <t>22,6; 29,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,66; 18,99</t>
+          <t>18,68; 25,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,29; 17,9</t>
+          <t>18,97; 24,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,66; 24,23</t>
+          <t>15,58; 22,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,88; 26,52</t>
+          <t>21,99; 26,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,85; 21,05</t>
+          <t>16,72; 20,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,26; 20,25</t>
+          <t>16,16; 20,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 27,93</t>
+          <t>15,27; 20,45</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24,47%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>23,81%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18,05%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>22,49%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,18%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>27,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,13; 29,35</t>
+          <t>22,4; 33,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,66; 23,6</t>
+          <t>12,48; 22,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,61; 27,88</t>
+          <t>19,6; 29,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 23,1</t>
+          <t>10,95; 20,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,58; 33,34</t>
+          <t>18,96; 29,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,55; 22,17</t>
+          <t>13,42; 24,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,77; 29,56</t>
+          <t>18,05; 28,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 21,54</t>
+          <t>11,63; 21,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,94; 29,52</t>
+          <t>21,74; 29,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,47; 21,05</t>
+          <t>14,46; 21,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,08; 27,25</t>
+          <t>19,77; 27,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,43; 20,18</t>
+          <t>12,66; 19,28</t>
         </is>
       </c>
     </row>
@@ -1069,39 +1069,39 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15,96%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20,33%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>21,96%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>17,88%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,76; 27,98</t>
+          <t>20,86; 25,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 22,68</t>
+          <t>13,78; 18,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,44; 24,57</t>
+          <t>14,58; 19,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,63; 34,39</t>
+          <t>14,19; 20,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,72; 25,89</t>
+          <t>22,8; 28,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 18,24</t>
+          <t>18,08; 22,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 18,89</t>
+          <t>19,51; 24,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,23</t>
+          <t>15,48; 20,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,41; 26,2</t>
+          <t>22,61; 26,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,46; 19,91</t>
+          <t>16,42; 19,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,7; 20,96</t>
+          <t>17,64; 21,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 25,82</t>
+          <t>15,47; 19,44</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17409</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10376</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11486</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22127</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>15730</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>12996</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16888</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17409</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10376</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7535</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>20546</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16458; 29014</t>
+          <t>11285; 23439</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10614; 22585</t>
+          <t>6270; 16313</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8330; 19447</t>
+          <t>3769; 12324</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9587; 30478</t>
+          <t>7009; 16998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12285; 23736</t>
+          <t>15608; 29612</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6063; 16218</t>
+          <t>10177; 22650</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3825; 12547</t>
+          <t>8320; 18962</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8679; 20357</t>
+          <t>5441; 14056</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30981; 49502</t>
+          <t>31572; 48512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18207; 33721</t>
+          <t>18696; 34685</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14377; 28457</t>
+          <t>14587; 28138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21483; 45587</t>
+          <t>14500; 27480</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>144</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>129</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>107513</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79312</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71303</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78081</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>108323</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>97610</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>102538</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>112812</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>107513</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79312</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71303</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91962</t>
+          <t>79352</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>157433</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94289; 123397</t>
+          <t>92625; 122391</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82659; 111240</t>
+          <t>66442; 93475</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89564; 117629</t>
+          <t>60160; 86275</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85871; 176869</t>
+          <t>63214; 103692</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94300; 122350</t>
+          <t>93853; 122046</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66771; 92834</t>
+          <t>83656; 111987</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59781; 87051</t>
+          <t>89327; 116954</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75371; 124536</t>
+          <t>67058; 94967</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>195113; 236447</t>
+          <t>196107; 236202</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>157831; 197125</t>
+          <t>156578; 195169</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>155657; 193825</t>
+          <t>154693; 193697</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>169247; 271527</t>
+          <t>138049; 184852</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>43225</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28759</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45566</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25778</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>41281</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>30110</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>38833</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25695</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>43225</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28759</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45566</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29610</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55306</t>
+          <t>49452</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33165; 50880</t>
+          <t>35277; 51984</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22783; 39364</t>
+          <t>21198; 37433</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30405; 48152</t>
+          <t>36495; 55373</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18460; 34545</t>
+          <t>18378; 34929</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35560; 52508</t>
+          <t>32871; 50977</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21316; 37647</t>
+          <t>22394; 40038</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36813; 55035</t>
+          <t>31167; 48618</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21715; 39336</t>
+          <t>17446; 31945</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>72573; 97671</t>
+          <t>71909; 98980</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48713; 70845</t>
+          <t>48672; 71801</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72069; 97788</t>
+          <t>70941; 99223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44611; 67025</t>
+          <t>40216; 61273</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>168147</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>171730</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>143451</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>154366</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>168147</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>118446</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>124404</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>154519; 189953</t>
+          <t>150318; 186420</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126031; 160032</t>
+          <t>102304; 135212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136692; 172716</t>
+          <t>107953; 140703</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123419; 227771</t>
+          <t>98906; 144738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>149294; 186591</t>
+          <t>154794; 190240</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>102240; 135423</t>
+          <t>127592; 161534</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108004; 139898</t>
+          <t>137167; 171263</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>115769; 168429</t>
+          <t>97094; 128435</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>313624; 366695</t>
+          <t>316501; 369737</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>238331; 288270</t>
+          <t>237765; 285685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>255509; 302504</t>
+          <t>254577; 303220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>254374; 366625</t>
+          <t>204898; 257387</t>
         </is>
       </c>
     </row>
